--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6021-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6021-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E158427-8E5D-40F5-A0A8-8EDA35C0C5DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4ACBFE73-BBE3-435B-B58F-906DBAA42B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{0C4F976A-0A81-48D2-811D-5BDA650CB9B4}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{7CE44563-38FE-4E7B-A7F1-00B3FA4FD427}"/>
   </bookViews>
   <sheets>
     <sheet name="6021-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1454,21 +1454,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D58E8633-10D3-4B45-9928-71154E6FAD0F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D82A6811-63B7-4772-B37D-7ADD7F71C79A}">
   <dimension ref="A1:R37"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9.33203125" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1496,7 +1496,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1526,7 +1526,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1572,7 +1572,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1622,7 +1622,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>7.88</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1732,7 +1732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>7.88</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2024</v>
       </c>
@@ -1842,7 +1842,7 @@
         <v>4.07</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1898,7 +1898,7 @@
         <v>2.31</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -1954,7 +1954,7 @@
         <v>1.76</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>2023</v>
       </c>
@@ -2008,7 +2008,7 @@
         <v>1.96</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
@@ -2064,7 +2064,7 @@
         <v>1.96</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2120,7 +2120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="39">
         <v>2022</v>
       </c>
@@ -2174,7 +2174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="37">
         <v>2021</v>
       </c>
@@ -2228,7 +2228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="39">
         <v>2020</v>
       </c>
@@ -2282,7 +2282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="37">
         <v>2019</v>
       </c>
@@ -2336,7 +2336,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="39">
         <v>2018</v>
       </c>
@@ -2390,7 +2390,7 @@
         <v>3.87</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="37">
         <v>2017</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2016</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="37">
         <v>2015</v>
       </c>
@@ -2552,7 +2552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="39">
         <v>2014</v>
       </c>
@@ -2606,7 +2606,7 @@
         <v>4.2699999999999996</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="37">
         <v>2013</v>
       </c>
@@ -2660,7 +2660,7 @@
         <v>2.71</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="39">
         <v>2012</v>
       </c>
@@ -2714,7 +2714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="37">
         <v>2011</v>
       </c>
@@ -2768,7 +2768,7 @@
         <v>9.43</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="39">
         <v>2010</v>
       </c>
@@ -2822,7 +2822,7 @@
         <v>2.94</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="37">
         <v>2009</v>
       </c>
@@ -2876,7 +2876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="39">
         <v>2008</v>
       </c>
@@ -2930,7 +2930,7 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="37">
         <v>2007</v>
       </c>
@@ -2984,7 +2984,7 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="39">
         <v>2006</v>
       </c>
@@ -3038,7 +3038,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="37">
         <v>2005</v>
       </c>
@@ -3092,7 +3092,7 @@
         <v>5.22</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="39">
         <v>2004</v>
       </c>
@@ -3146,7 +3146,7 @@
         <v>7.58</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="37">
         <v>2003</v>
       </c>
@@ -3200,7 +3200,7 @@
         <v>6.67</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="39">
         <v>2002</v>
       </c>
@@ -3254,7 +3254,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="37">
         <v>2001</v>
       </c>
@@ -3308,7 +3308,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="39">
         <v>2000</v>
       </c>
@@ -3362,7 +3362,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="37" t="s">
         <v>37</v>
       </c>
